--- a/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-22.xlsx
+++ b/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-22.xlsx
@@ -474,697 +474,697 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>5583986161095</v>
+        <v>5583986344505</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chris de Oliveira Guedes</t>
+          <t>Carlos Antonio Cordeiro de Sousa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>5583988822973</v>
+        <v>5583996891137</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Marinalva</t>
+          <t>Residencial</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Marinalva da Silva Santos</t>
+          <t>Residencial Florenca</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>5583988460931</v>
+        <v>5543999709926</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Edmilson</t>
+          <t>Rafael</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Edmilson da Silva Santos Junior</t>
+          <t>Rafael Campos</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>5583987142174</v>
+        <v>5583988044505</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gideildo</t>
+          <t>Rodolfo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Gideildo de Lima Ferreira</t>
+          <t>Rodolfo Hiroshi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>5583988209018</v>
+        <v>5583988220845</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Manoel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Angela Carla Almeida de Souza</t>
+          <t>Manoel Rodrigues de S Filho</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>5583988429214</v>
+        <v>5583993828124</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Thais</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thais Carneiro</t>
+          <t>Jose Wellington Freitas</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>5583987094881</v>
+        <v>5583988033861</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sergio</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sergio de Oliveira Silva</t>
+          <t>Vitoria Jaqueline Fernandes da Fonseca</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>5583988280911</v>
+        <v>5521983043465</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Claudio</t>
+          <t>Ernades</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Claudio Jose Silva de Carvalho</t>
+          <t>Ernades Datas da Silva</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>5583996031383</v>
+        <v>5583998245941</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Carla</t>
+          <t>Marcelo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Carla Lima Novo Barbosa</t>
+          <t>Marcelo da Fonseca Silva</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>5583987467567</v>
+        <v>5583988816212</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Edson</t>
+          <t>Wg</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Edson Santos</t>
+          <t>Wg Refrigeracao</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>5583987380219</v>
+        <v>5583981179397</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Francisco</t>
+          <t>Airton</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Francisco Judivan de Medeiros</t>
+          <t>Airton Barbosa de Araujo Liberato</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>5583996018819</v>
+        <v>5583991665028</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Emmanuelle</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Maria da Conceicao de Brito Silva</t>
+          <t>Emmanuelle Pereira</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>5583988522764</v>
+        <v>5583988911246</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jair</t>
+          <t>Lucio</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jair Januario</t>
+          <t>Lucio Carvalho Machado</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>5583988952526</v>
+        <v>5583987849457</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fernando</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fernando Morais</t>
+          <t>Ana Cristina Lima Bezerra</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>5583988751420</v>
+        <v>5583987687054</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cicero</t>
+          <t>Clemilde</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cicero Ferreira de Souza</t>
+          <t>Clemilde dos Santos Falcao</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>5583981961973</v>
+        <v>5583991306557</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Jonhdiego</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jose Helio Bezerra da Silva</t>
+          <t>Jonhdiego dos Santos Silva</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>5583998094883</v>
+        <v>5583993421999</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jorge</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jorge Luis Mena</t>
+          <t>Maria de Lourdes dos Santos Miranda</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>5583988278310</v>
+        <v>5583996068960</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lucas Motos Peças</t>
+          <t>Maria de Fatima Maia Pessoa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>5583987060662</v>
+        <v>5583986161095</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pablo</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pablo Emanoel Soares de Castro</t>
+          <t>Chris de Oliveira Guedes</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="3">
       <c r="A21" s="4" t="n">
-        <v>5583998780155</v>
+        <v>5583988822973</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sergio</t>
+          <t>Marinalva</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sergio Ricardo Soares Caetano</t>
+          <t>Marinalva da Silva Santos</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="3">
       <c r="A22" s="4" t="n">
-        <v>5548999338873</v>
+        <v>5583988460931</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Edmilson</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jose Jurandi Vieira</t>
+          <t>Edmilson da Silva Santos Junior</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="3">
       <c r="A23" s="4" t="n">
-        <v>5583991255141</v>
+        <v>5583987142174</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Josemar</t>
+          <t>Gideildo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Josemar Maximo N Junior</t>
+          <t>Gideildo de Lima Ferreira</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="3">
       <c r="A24" s="4" t="n">
-        <v>5583987292967</v>
+        <v>5583988209018</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Samela</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Samela Laurane Gomes Pontes</t>
+          <t>Angela Carla Almeida de Souza</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="3">
       <c r="A25" s="4" t="n">
-        <v>5583988566880</v>
+        <v>5583988429214</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Thais</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jose Carlos de Araujo</t>
+          <t>Thais Carneiro</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="3">
       <c r="A26" s="4" t="n">
-        <v>5583999043407</v>
+        <v>5583987094881</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Marcio</t>
+          <t>Sergio</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Marcio Ricardo Sousa Nunes</t>
+          <t>Sergio de Oliveira Silva</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="3">
       <c r="A27" s="4" t="n">
-        <v>5583999176197</v>
+        <v>5583988280911</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Marina</t>
+          <t>Claudio</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Marina Santana</t>
+          <t>Claudio Jose Silva de Carvalho</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="3">
       <c r="A28" s="4" t="n">
-        <v>5583996374518</v>
+        <v>5583996031383</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Gerlandia</t>
+          <t>Carla</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Gerlandia Albino Filomeno Romeu</t>
+          <t>Carla Lima Novo Barbosa</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="3">
       <c r="A29" s="4" t="n">
-        <v>5583988732945</v>
+        <v>5583987467567</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Joselio</t>
+          <t>Edson</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Joselio Bento do Nascimento</t>
+          <t>Edson Santos</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="3">
       <c r="A30" s="4" t="n">
-        <v>5583981724945</v>
+        <v>5583987380219</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Francisco</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jose Erielson Almeida do Nascimento</t>
+          <t>Francisco Judivan de Medeiros</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="3">
       <c r="A31" s="4" t="n">
-        <v>5583986720595</v>
+        <v>5583996018819</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Livia</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Livia Ramos</t>
+          <t>Maria da Conceicao de Brito Silva</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="3">
       <c r="A32" s="4" t="n">
-        <v>5583986602392</v>
+        <v>5583988522764</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Alessandro</t>
+          <t>Jair</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Alessandro Gomes de Almeida</t>
+          <t>Jair Januario</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="3">
       <c r="A33" s="4" t="n">
-        <v>5583991856192</v>
+        <v>5583988952526</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Manoel</t>
+          <t>Fernando</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Manoel Francisco dos Santos</t>
+          <t>Fernando Morais</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="3">
       <c r="A34" s="4" t="n">
-        <v>5583987558685</v>
+        <v>5583988751420</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cristiane</t>
+          <t>Cicero</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cristiane Felix da Silva Santos</t>
+          <t>Cicero Ferreira de Souza</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="3">
       <c r="A35" s="4" t="n">
-        <v>5583996998233</v>
+        <v>5583981961973</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tania</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tania do Carmo Pessoa</t>
+          <t>Jose Helio Bezerra da Silva</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="3">
       <c r="A36" s="4" t="n">
-        <v>5583986610779</v>
+        <v>5583998094883</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Jean</t>
+          <t>Jorge</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jean Kleber Santos da Silva</t>
+          <t>Jorge Luis Mena</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="3">
       <c r="A37" s="4" t="n">
-        <v>5511910916798</v>
+        <v>5583988278310</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Innovasan</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Innovasan</t>
+          <t>Lucas Motos Peças</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="3">
       <c r="A38" s="4" t="n">
-        <v>5592991914004</v>
+        <v>5583987060662</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Manoel</t>
+          <t>Pablo</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Manoel Espinola</t>
+          <t>Pablo Emanoel Soares de Castro</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="3">
       <c r="A39" s="4" t="n">
-        <v>5583986855845</v>
+        <v>5583998780155</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Jonatha</t>
+          <t>Sergio</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jonatha Ferreira da Silva</t>
+          <t>Sergio Ricardo Soares Caetano</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="3">
       <c r="A40" s="4" t="n">
-        <v>5583988409906</v>
+        <v>5548999338873</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Charles Eduardo Soares de Oliveira</t>
+          <t>Jose Jurandi Vieira</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="3">
       <c r="A41" s="4" t="n">
-        <v>5583999685044</v>
+        <v>5583991255141</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Edgar</t>
+          <t>Josemar</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Edgar Luis Almeida da Silva</t>
+          <t>Josemar Maximo N Junior</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="3">
       <c r="A42" s="4" t="n">
-        <v>5583987295739</v>
+        <v>5583987292967</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tiago</t>
+          <t>Samela</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tiago Justino</t>
+          <t>Samela Laurane Gomes Pontes</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="3">
       <c r="A43" s="4" t="n">
-        <v>5583988388764</v>
+        <v>5583988566880</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Aluisio</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Aluisio Ferreira de Santana Filho</t>
+          <t>Jose Carlos de Araujo</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="3">
       <c r="A44" s="4" t="n">
-        <v>5583991741951</v>
+        <v>5583999043407</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Residencial</t>
+          <t>Marcio</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Residencial Florenca Ii</t>
+          <t>Marcio Ricardo Sousa Nunes</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="3">
       <c r="A45" s="4" t="n">
-        <v>5583996158493</v>
+        <v>5583999176197</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Adriana</t>
+          <t>Marina</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Adriana Almeida Martins</t>
+          <t>Marina Santana</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="3">
       <c r="A46" s="4" t="n">
-        <v>5583987264017</v>
+        <v>5583996374518</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ug-</t>
+          <t>Gerlandia</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ug- Construtora</t>
+          <t>Gerlandia Albino Filomeno Romeu</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="3">
       <c r="A47" s="4" t="n">
-        <v>5583986951266</v>
+        <v>5583988732945</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Severino</t>
+          <t>Joselio</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Severino Gomes Bezerra</t>
+          <t>Joselio Bento do Nascimento</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="3">
       <c r="A48" s="4" t="n">
-        <v>5583986592015</v>
+        <v>5583981724945</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -1173,52 +1173,52 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jose Humberto da Luz Ferreira</t>
+          <t>Jose Erielson Almeida do Nascimento</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="3">
       <c r="A49" s="4" t="n">
-        <v>5583987036171</v>
+        <v>5583986720595</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Rosilma</t>
+          <t>Livia</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Rosilma Dias dos Santos</t>
+          <t>Livia Ramos</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="3">
       <c r="A50" s="4" t="n">
-        <v>5531992069031</v>
+        <v>5583986602392</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Bernardo</t>
+          <t>Alessandro</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bernardo Augusto Diniz</t>
+          <t>Alessandro Gomes de Almeida</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="3">
       <c r="A51" s="4" t="n">
-        <v>5583999779815</v>
+        <v>5583991856192</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Marilene</t>
+          <t>Manoel</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Marilene Lins Dias</t>
+          <t>Manoel Francisco dos Santos</t>
         </is>
       </c>
     </row>
